--- a/Config/Datas/StickDatas/StickDatas.xlsx
+++ b/Config/Datas/StickDatas/StickDatas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\BBQ\Config\Datas\StickDatas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\StickDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EBF5B5-1820-4E03-A066-438E93478AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BFDC8A-B21F-4E2D-81F7-37FF01CD3EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,6 +116,14 @@
   </si>
   <si>
     <t>iron</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxFoodCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -475,13 +483,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="14.125" customWidth="1"/>
+    <col min="4" max="5" width="14.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,14 +503,17 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -516,15 +527,18 @@
         <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="2"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -537,14 +551,15 @@
       <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -554,14 +569,17 @@
       <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>22</v>
       </c>
@@ -571,10 +589,13 @@
       <c r="D5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>20</v>
       </c>
     </row>

--- a/Config/Datas/StickDatas/StickDatas.xlsx
+++ b/Config/Datas/StickDatas/StickDatas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\StickDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BFDC8A-B21F-4E2D-81F7-37FF01CD3EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B21B04-8850-4D72-854C-914CC26EF83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -124,6 +124,18 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>short</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短签</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是一根短签</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -483,13 +495,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="5" width="14.08203125" customWidth="1"/>
+    <col min="4" max="5" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -513,7 +525,7 @@
       </c>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -538,7 +550,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -559,7 +571,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -579,7 +591,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>22</v>
       </c>
@@ -590,12 +602,32 @@
         <v>12</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
         <v>20</v>
       </c>
     </row>

--- a/Config/Datas/StickDatas/StickDatas.xlsx
+++ b/Config/Datas/StickDatas/StickDatas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\StickDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B21B04-8850-4D72-854C-914CC26EF83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDD38C3-2B31-4C86-BE17-BD24DEA27062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -136,6 +136,22 @@
   </si>
   <si>
     <t>这是一根短签</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>originCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effectDescription</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这根签的时间消耗不会增长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BBQ_2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -495,13 +511,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="5" width="14.125" customWidth="1"/>
+    <col min="4" max="4" width="14.125" customWidth="1"/>
+    <col min="5" max="5" width="22.5" customWidth="1"/>
+    <col min="6" max="7" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -515,17 +533,23 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -539,18 +563,24 @@
         <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="2"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -564,14 +594,16 @@
         <v>9</v>
       </c>
       <c r="E3" s="1"/>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
       <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -581,17 +613,20 @@
       <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="E4">
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
         <v>6</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>17</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>22</v>
       </c>
@@ -601,17 +636,20 @@
       <c r="D5" t="s">
         <v>12</v>
       </c>
-      <c r="E5">
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
         <v>8</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>17</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
@@ -621,14 +659,20 @@
       <c r="D6" t="s">
         <v>27</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
         <v>4</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>17</v>
       </c>
-      <c r="G6" t="s">
-        <v>20</v>
+      <c r="I6" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
